--- a/data/trans_dic/P20B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Clase-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>13,2; 54,29</t>
+          <t>14,41; 52,5</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,04; 57,77</t>
+          <t>9,21; 54,34</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>16,14; 57,32</t>
+          <t>18,18; 57,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>26,08; 60,27</t>
+          <t>27,06; 61,48</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,71; 36,07</t>
+          <t>4,78; 35,75</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>10,56; 42,94</t>
+          <t>12,33; 44,98</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,62</t>
+          <t>0,0; 24,1</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,51; 21,01</t>
+          <t>4,04; 22,64</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,6; 38,99</t>
+          <t>11,85; 39,54</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>16,17; 42,18</t>
+          <t>14,47; 41,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11,15; 33,72</t>
+          <t>10,89; 32,49</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,54; 36,91</t>
+          <t>17,18; 37,92</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,21; 43,74</t>
+          <t>5,02; 42,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 32,14</t>
+          <t>0,0; 36,13</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,72; 40,71</t>
+          <t>4,82; 40,58</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>14,93; 53,91</t>
+          <t>16,16; 53,52</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,25; 29,49</t>
+          <t>3,38; 30,14</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,37; 30,97</t>
+          <t>3,16; 31,01</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,7; 44,13</t>
+          <t>11,76; 44,14</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>15,24; 45,68</t>
+          <t>14,76; 45,1</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,62; 28,32</t>
+          <t>6,6; 30,78</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,21; 23,05</t>
+          <t>4,59; 24,79</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,65; 37,31</t>
+          <t>12,39; 36,23</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>18,59; 41,69</t>
+          <t>19,68; 42,9</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,68; 58,24</t>
+          <t>18,84; 61,41</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,32; 46,8</t>
+          <t>17,3; 45,63</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,33; 53,14</t>
+          <t>18,6; 53,48</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>30,01; 61,47</t>
+          <t>28,23; 63,65</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,69; 42,46</t>
+          <t>4,84; 43,36</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,32; 52,04</t>
+          <t>13,1; 49,18</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>18,21; 70,52</t>
+          <t>19,55; 72,28</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>10,67; 50,56</t>
+          <t>11,0; 49,83</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,58; 42,84</t>
+          <t>15,41; 45,46</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>19,9; 41,84</t>
+          <t>18,74; 41,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24,11; 52,06</t>
+          <t>23,94; 52,35</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>25,55; 53,29</t>
+          <t>26,34; 53,12</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,57; 34,77</t>
+          <t>12,8; 34,19</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,85; 43,33</t>
+          <t>20,76; 43,83</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>27,27; 54,09</t>
+          <t>26,6; 55,72</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,48; 35,37</t>
+          <t>14,7; 35,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,62; 30,6</t>
+          <t>11,37; 30,17</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 29,86</t>
+          <t>10,51; 28,77</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>11,34; 29,94</t>
+          <t>10,69; 30,21</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,97; 27,26</t>
+          <t>10,04; 27,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>14,1; 27,73</t>
+          <t>13,86; 28,24</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 32,81</t>
+          <t>18,68; 32,81</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,14; 36,91</t>
+          <t>20,77; 36,94</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,77; 29,03</t>
+          <t>14,43; 28,37</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,67; 56,26</t>
+          <t>11,44; 56,71</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>20,37; 52,43</t>
+          <t>19,98; 52,89</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18,47; 61,36</t>
+          <t>19,75; 58,46</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19,39; 47,39</t>
+          <t>18,1; 46,68</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>11,13; 38,28</t>
+          <t>10,9; 36,28</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,07; 46,57</t>
+          <t>24,67; 48,34</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,31; 57,19</t>
+          <t>26,47; 55,18</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,38; 44,35</t>
+          <t>21,04; 44,62</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>13,49; 36,2</t>
+          <t>14,07; 35,61</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>25,41; 45,73</t>
+          <t>26,66; 44,33</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>26,45; 51,45</t>
+          <t>27,35; 51,76</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,94; 41,58</t>
+          <t>23,42; 41,87</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,99; 75,81</t>
+          <t>11,94; 75,93</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,35</t>
+          <t>0,0; 47,77</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 89,03</t>
+          <t>0,0; 75,98</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,27; 35,41</t>
+          <t>16,29; 35,0</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,01; 35,15</t>
+          <t>15,11; 34,39</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,49; 34,98</t>
+          <t>12,28; 33,65</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>13,32; 43,81</t>
+          <t>12,66; 42,16</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,25; 35,32</t>
+          <t>16,35; 33,8</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,86; 34,94</t>
+          <t>16,66; 33,89</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>12,18; 32,96</t>
+          <t>11,52; 32,24</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,27; 43,03</t>
+          <t>13,06; 42,73</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>18,86; 34,1</t>
+          <t>19,5; 34,22</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,64; 37,4</t>
+          <t>23,43; 36,98</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>26,16; 40,84</t>
+          <t>25,74; 41,36</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,87; 40,2</t>
+          <t>26,44; 39,76</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 25,34</t>
+          <t>14,8; 25,0</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>20,23; 30,31</t>
+          <t>19,85; 29,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>19,18; 29,62</t>
+          <t>18,85; 30,21</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>17,96; 29,29</t>
+          <t>18,2; 28,63</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,3; 26,69</t>
+          <t>18,71; 26,79</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>23,04; 30,85</t>
+          <t>22,82; 31,4</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,44; 32,62</t>
+          <t>23,71; 32,97</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,72; 32,22</t>
+          <t>23,73; 32,36</t>
         </is>
       </c>
     </row>
@@ -1669,7 +1669,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que estuvo en lista de espera por ingreso hospitalario</t>
+          <t>Población que estuvo en lista de espera por ingreso hospitalario (tasa de respuesta: 99,41%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3128; 12862</t>
+          <t>3413; 12439</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2340; 12240</t>
+          <t>1950; 11513</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4230; 15025</t>
+          <t>4764; 14956</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8134; 18802</t>
+          <t>8441; 19180</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>900; 6901</t>
+          <t>915; 6841</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>3453; 14044</t>
+          <t>4034; 14711</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7982</t>
+          <t>0; 7814</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1105; 6612</t>
+          <t>1273; 7125</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>4967; 16696</t>
+          <t>5076; 16933</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>8715; 22730</t>
+          <t>7797; 22610</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6538; 19772</t>
+          <t>6386; 19052</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10992; 23131</t>
+          <t>10769; 23764</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>798; 6692</t>
+          <t>768; 6559</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 5431</t>
+          <t>0; 6106</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>969; 8358</t>
+          <t>991; 8333</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3243; 11708</t>
+          <t>3509; 11621</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>952; 8645</t>
+          <t>990; 8837</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1122; 10318</t>
+          <t>1053; 10333</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3567; 14714</t>
+          <t>3920; 14716</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4391; 13159</t>
+          <t>4252; 12994</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2951; 12637</t>
+          <t>2944; 13731</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2114; 11577</t>
+          <t>2307; 12451</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6279; 20097</t>
+          <t>6674; 19519</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9392; 21062</t>
+          <t>9945; 21675</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3708; 11559</t>
+          <t>3740; 12188</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8799; 22481</t>
+          <t>8312; 21923</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5849; 16957</t>
+          <t>5934; 17066</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9552; 19564</t>
+          <t>8985; 20258</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>776; 7026</t>
+          <t>800; 7175</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3055; 11935</t>
+          <t>3003; 11278</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2913; 11278</t>
+          <t>3127; 11560</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1681; 7963</t>
+          <t>1733; 7848</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5671; 15592</t>
+          <t>5610; 16544</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14124; 29693</t>
+          <t>13300; 29645</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11550; 24937</t>
+          <t>11468; 25078</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12154; 25355</t>
+          <t>12532; 25272</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7085; 19600</t>
+          <t>7213; 19272</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15359; 31917</t>
+          <t>15288; 32279</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14436; 28635</t>
+          <t>14080; 29496</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8690; 21231</t>
+          <t>8826; 21244</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6593; 18990</t>
+          <t>7058; 18724</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>9004; 23713</t>
+          <t>8344; 22847</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8484; 22405</t>
+          <t>7996; 22601</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5207; 14237</t>
+          <t>5242; 14112</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16696; 32844</t>
+          <t>16417; 33443</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28702; 50219</t>
+          <t>28593; 50228</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25735; 47162</t>
+          <t>26536; 47199</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16574; 32589</t>
+          <t>16202; 31845</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1768; 8526</t>
+          <t>1734; 8595</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7761; 19973</t>
+          <t>7613; 20150</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4038; 13412</t>
+          <t>4317; 12778</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7698; 18817</t>
+          <t>7186; 18533</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4560; 15679</t>
+          <t>4463; 14858</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19025; 36806</t>
+          <t>19503; 38208</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12760; 26716</t>
+          <t>12368; 25777</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8898; 18459</t>
+          <t>8758; 18571</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7568; 20309</t>
+          <t>7896; 19980</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>29767; 53572</t>
+          <t>31234; 51933</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18141; 35282</t>
+          <t>18758; 35493</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19467; 33812</t>
+          <t>19048; 34052</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>944; 5973</t>
+          <t>941; 5983</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4274</t>
+          <t>0; 4311</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2567</t>
+          <t>0; 2191</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13075; 28449</t>
+          <t>13093; 28124</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12757; 29864</t>
+          <t>12841; 29217</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8270; 23169</t>
+          <t>8134; 22290</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5403; 17774</t>
+          <t>5137; 17105</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13645; 29662</t>
+          <t>13733; 28383</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15650; 32442</t>
+          <t>15465; 31469</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>9169; 24809</t>
+          <t>8671; 24268</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5766; 18695</t>
+          <t>5672; 18566</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>25274; 45688</t>
+          <t>26122; 45854</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48649; 76947</t>
+          <t>48214; 76082</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>42502; 66360</t>
+          <t>41819; 67203</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>50338; 75315</t>
+          <t>49540; 74487</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>38941; 62932</t>
+          <t>36755; 62079</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>67250; 100738</t>
+          <t>65961; 98844</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>51703; 79847</t>
+          <t>50800; 81415</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>37799; 61642</t>
+          <t>38307; 60255</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>69951; 102057</t>
+          <t>71546; 102438</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>123981; 166002</t>
+          <t>122828; 168984</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>101246; 140920</t>
+          <t>102423; 142450</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94374; 128147</t>
+          <t>94406; 128721</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P20B-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P20B-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>42,53%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,4%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>25,62%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>14,41; 52,5</t>
+          <t>13,18; 53,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,21; 54,34</t>
+          <t>9,79; 55,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>18,18; 57,06</t>
+          <t>18,66; 60,04</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>27,06; 61,48</t>
+          <t>25,72; 61,16</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>4,78; 35,75</t>
+          <t>4,7; 36,29</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,33; 44,98</t>
+          <t>10,76; 43,68</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,1</t>
+          <t>0,0; 23,42</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>4,04; 22,64</t>
+          <t>3,77; 20,59</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>11,85; 39,54</t>
+          <t>12,49; 39,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,47; 41,95</t>
+          <t>16,04; 41,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,89; 32,49</t>
+          <t>11,05; 32,57</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>17,18; 37,92</t>
+          <t>16,45; 37,33</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>32,88%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>29,5%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>29,41%</t>
+          <t>30,9%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 42,87</t>
+          <t>5,28; 43,32</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,13</t>
+          <t>0,0; 30,44</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4,82; 40,58</t>
+          <t>5,21; 41,38</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16,16; 53,52</t>
+          <t>15,76; 53,58</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>3,38; 30,14</t>
+          <t>3,4; 30,71</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3,16; 31,01</t>
+          <t>3,33; 28,99</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>11,76; 44,14</t>
+          <t>11,95; 45,85</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>14,76; 45,1</t>
+          <t>17,06; 45,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>6,6; 30,78</t>
+          <t>6,57; 29,46</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,59; 24,79</t>
+          <t>5,14; 24,73</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12,39; 36,23</t>
+          <t>11,8; 37,43</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>19,68; 42,9</t>
+          <t>20,89; 43,79</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>45,2%</t>
+          <t>47,81%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>25,67%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>39,43%</t>
+          <t>40,46%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>18,84; 61,41</t>
+          <t>18,75; 61,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>17,3; 45,63</t>
+          <t>18,08; 46,07</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>18,6; 53,48</t>
+          <t>18,26; 52,84</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>28,23; 63,65</t>
+          <t>31,69; 63,81</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>4,84; 43,36</t>
+          <t>4,88; 43,42</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>13,1; 49,18</t>
+          <t>13,09; 49,84</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>19,55; 72,28</t>
+          <t>15,21; 74,08</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,0; 49,83</t>
+          <t>9,88; 46,65</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>15,41; 45,46</t>
+          <t>15,33; 42,98</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18,74; 41,77</t>
+          <t>19,87; 42,77</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23,94; 52,35</t>
+          <t>22,25; 51,02</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>26,34; 53,12</t>
+          <t>28,55; 53,67</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>23,86%</t>
+          <t>22,92%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>17,03%</t>
+          <t>17,62%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,68%</t>
+          <t>20,34%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,8; 34,19</t>
+          <t>12,84; 34,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>20,76; 43,83</t>
+          <t>21,13; 43,95</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>26,6; 55,72</t>
+          <t>25,98; 53,47</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14,7; 35,39</t>
+          <t>13,8; 33,96</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,37; 30,17</t>
+          <t>10,5; 29,75</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,51; 28,77</t>
+          <t>11,59; 29,4</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,69; 30,21</t>
+          <t>11,99; 31,65</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>10,04; 27,02</t>
+          <t>10,26; 26,18</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>13,86; 28,24</t>
+          <t>13,83; 28,17</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>18,68; 32,81</t>
+          <t>18,33; 31,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20,77; 36,94</t>
+          <t>20,33; 37,21</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,43; 28,37</t>
+          <t>14,78; 27,91</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>32,26%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,27 +1244,27 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
+          <t>33,2%</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>23,87%</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>35,19%</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>39,29%</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
           <t>32,45%</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>23,87%</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>35,19%</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>39,29%</t>
-        </is>
-      </c>
-      <c r="N12" s="2" t="inlineStr">
-        <is>
-          <t>32,36%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>11,44; 56,71</t>
+          <t>11,28; 55,07</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>19,98; 52,89</t>
+          <t>19,98; 53,56</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19,75; 58,46</t>
+          <t>18,88; 60,3</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18,1; 46,68</t>
+          <t>19,9; 46,75</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>10,9; 36,28</t>
+          <t>11,51; 36,44</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>24,67; 48,34</t>
+          <t>25,68; 46,58</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>26,47; 55,18</t>
+          <t>26,46; 55,87</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>21,04; 44,62</t>
+          <t>22,54; 45,32</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>14,07; 35,61</t>
+          <t>13,41; 35,34</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>26,66; 44,33</t>
+          <t>25,97; 44,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27,35; 51,76</t>
+          <t>27,7; 51,63</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>23,42; 41,87</t>
+          <t>24,51; 42,55</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>18,07%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>24,48%</t>
+          <t>24,63%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24,06%</t>
+          <t>23,55%</t>
         </is>
       </c>
     </row>
@@ -1422,57 +1422,57 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,94; 75,93</t>
+          <t>12,05; 75,98</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 47,77</t>
+          <t>0,0; 56,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,98</t>
+          <t>0,0; 97,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>16,29; 35,0</t>
+          <t>16,21; 35,06</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>15,11; 34,39</t>
+          <t>14,14; 34,19</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>12,28; 33,65</t>
+          <t>12,77; 34,48</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>12,66; 42,16</t>
+          <t>13,38; 43,41</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16,35; 33,8</t>
+          <t>16,49; 34,68</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>16,66; 33,89</t>
+          <t>17,08; 34,54</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11,52; 32,24</t>
+          <t>12,34; 32,75</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>13,06; 42,73</t>
+          <t>13,17; 41,75</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>33,24%</t>
+          <t>33,37%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>23,14%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>27,69%</t>
+          <t>27,86%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>19,5; 34,22</t>
+          <t>19,75; 33,9</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>23,43; 36,98</t>
+          <t>23,64; 36,92</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>25,74; 41,36</t>
+          <t>26,65; 42,15</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>26,44; 39,76</t>
+          <t>26,71; 40,13</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>14,8; 25,0</t>
+          <t>15,55; 25,58</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>19,85; 29,74</t>
+          <t>20,1; 29,65</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>18,85; 30,21</t>
+          <t>19,59; 30,26</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>18,2; 28,63</t>
+          <t>18,42; 28,5</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>18,71; 26,79</t>
+          <t>18,4; 26,81</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>22,82; 31,4</t>
+          <t>22,97; 30,53</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23,71; 32,97</t>
+          <t>23,57; 32,47</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>23,73; 32,36</t>
+          <t>23,7; 31,91</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13357</t>
+          <t>13925</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3208</t>
+          <t>3779</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>17704</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3413; 12439</t>
+          <t>3122; 12788</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1950; 11513</t>
+          <t>2074; 11715</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4764; 14956</t>
+          <t>4890; 15738</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>8441; 19180</t>
+          <t>8422; 20025</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>915; 6841</t>
+          <t>899; 6944</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>4034; 14711</t>
+          <t>3518; 14287</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 7814</t>
+          <t>0; 7593</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1273; 7125</t>
+          <t>1369; 7485</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>5076; 16933</t>
+          <t>5348; 16897</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7797; 22610</t>
+          <t>8646; 22503</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>6386; 19052</t>
+          <t>6477; 19096</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>10769; 23764</t>
+          <t>11369; 25797</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7716</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7978</t>
+          <t>9799</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>14859</t>
+          <t>17516</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>768; 6559</t>
+          <t>808; 6628</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0; 6106</t>
+          <t>0; 5143</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>991; 8333</t>
+          <t>1069; 8497</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3509; 11621</t>
+          <t>3699; 12572</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>990; 8837</t>
+          <t>995; 9003</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1053; 10333</t>
+          <t>1109; 9660</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>3920; 14716</t>
+          <t>3983; 15287</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4252; 12994</t>
+          <t>5667; 15196</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2944; 13731</t>
+          <t>2931; 13142</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2307; 12451</t>
+          <t>2580; 12421</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>6674; 19519</t>
+          <t>6357; 20166</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>9945; 21675</t>
+          <t>11840; 24820</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14387</t>
+          <t>17659</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>4372</t>
+          <t>4711</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>18758</t>
+          <t>22370</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>3740; 12188</t>
+          <t>3720; 12230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>8312; 21923</t>
+          <t>8684; 22131</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>5934; 17066</t>
+          <t>5826; 16860</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>8985; 20258</t>
+          <t>11703; 23566</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>800; 7175</t>
+          <t>808; 7185</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>3003; 11278</t>
+          <t>3003; 11430</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3127; 11560</t>
+          <t>2433; 11848</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>1733; 7848</t>
+          <t>1813; 8561</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>5610; 16544</t>
+          <t>5578; 15645</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>13300; 29645</t>
+          <t>14100; 30359</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11468; 25078</t>
+          <t>10661; 24442</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>12532; 25272</t>
+          <t>15783; 29670</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14322</t>
+          <t>14435</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>8894</t>
+          <t>10534</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>23216</t>
+          <t>24969</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7213; 19272</t>
+          <t>7236; 19626</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>15288; 32279</t>
+          <t>15563; 32372</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>14080; 29496</t>
+          <t>13754; 28304</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>8826; 21244</t>
+          <t>8690; 21386</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>7058; 18724</t>
+          <t>6515; 18463</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>8344; 22847</t>
+          <t>9201; 23345</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7996; 22601</t>
+          <t>8974; 23683</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5242; 14112</t>
+          <t>6136; 15655</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>16417; 33443</t>
+          <t>16377; 33361</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>28593; 50228</t>
+          <t>28059; 48971</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26536; 47199</t>
+          <t>25973; 47535</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16202; 31845</t>
+          <t>18150; 34264</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12809</t>
+          <t>13960</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>13503</t>
+          <t>15535</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>26312</t>
+          <t>29495</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1734; 8595</t>
+          <t>1709; 8346</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>7613; 20150</t>
+          <t>7613; 20406</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>4317; 12778</t>
+          <t>4126; 13181</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>7186; 18533</t>
+          <t>8778; 20619</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>4463; 14858</t>
+          <t>4713; 14923</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>19503; 38208</t>
+          <t>20299; 36817</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>12368; 25777</t>
+          <t>12362; 26101</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>8758; 18571</t>
+          <t>10548; 21205</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>7896; 19980</t>
+          <t>7524; 19830</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>31234; 51933</t>
+          <t>30416; 52077</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18758; 35493</t>
+          <t>18992; 35402</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>19048; 34052</t>
+          <t>22279; 38676</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>521</t>
+          <t>507</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>9931</t>
+          <t>10809</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>10452</t>
+          <t>11317</t>
         </is>
       </c>
     </row>
@@ -2972,57 +2972,57 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>941; 5983</t>
+          <t>949; 5986</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 4311</t>
+          <t>0; 5096</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 2191</t>
+          <t>0; 4065</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>13093; 28124</t>
+          <t>13022; 28169</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>12841; 29217</t>
+          <t>12019; 29047</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8134; 22290</t>
+          <t>8458; 22837</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>5137; 17105</t>
+          <t>5875; 19052</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>13733; 28383</t>
+          <t>13843; 29123</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>15465; 31469</t>
+          <t>15862; 32068</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>8671; 24268</t>
+          <t>9288; 24651</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>5672; 18566</t>
+          <t>6329; 20061</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>62277</t>
+          <t>68202</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>47886</t>
+          <t>55168</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>110162</t>
+          <t>123370</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>26122; 45854</t>
+          <t>26457; 45426</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>48214; 76082</t>
+          <t>48631; 75956</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>41819; 67203</t>
+          <t>43294; 68491</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49540; 74487</t>
+          <t>54583; 82018</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>36755; 62079</t>
+          <t>38624; 63528</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>65961; 98844</t>
+          <t>66810; 98551</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>50800; 81415</t>
+          <t>52809; 81571</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>38307; 60255</t>
+          <t>43909; 67943</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>71546; 102438</t>
+          <t>70362; 102503</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>122828; 168984</t>
+          <t>123610; 164299</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>102423; 142450</t>
+          <t>101805; 140282</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>94406; 128721</t>
+          <t>104931; 141284</t>
         </is>
       </c>
     </row>
